--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104508_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104508_W6.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.788</v>
+        <v>5.0526</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5406</v>
+        <v>4.2332</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2474</v>
+        <v>0.8194</v>
       </c>
       <c r="G2" t="n">
-        <v>6.1581</v>
+        <v>6.1696</v>
       </c>
       <c r="H2" t="n">
-        <v>7.3895</v>
+        <v>7.3844</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.2313</v>
+        <v>-1.2148</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1038</v>
+        <v>6.0722</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4721</v>
+        <v>5.4468</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6317</v>
+        <v>0.6254</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0543</v>
+        <v>0.0974</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9174</v>
+        <v>1.9375</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.863</v>
+        <v>-1.8402</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4381</v>
+        <v>-1.1853</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0434</v>
+        <v>-0.3139</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3947</v>
+        <v>-0.8714</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9441</v>
+        <v>3.3054</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7438</v>
+        <v>2.2296</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2003</v>
+        <v>1.0757</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0569</v>
+        <v>2.0747</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1932</v>
+        <v>1.2029</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8637</v>
+        <v>0.8718</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5785</v>
+        <v>2.5713</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6754</v>
+        <v>0.6722</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9032</v>
+        <v>1.8991</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5216</v>
+        <v>-0.4967</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3111</v>
+        <v>-0.9789</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8347</v>
+        <v>-0.3417</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4764</v>
+        <v>-0.6372</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6175</v>
+        <v>3.0281</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6137</v>
+        <v>1.4083</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0038</v>
+        <v>1.6199</v>
       </c>
       <c r="G4" t="n">
-        <v>1.299</v>
+        <v>-0.3242</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1097</v>
+        <v>-0.8558</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1893</v>
+        <v>0.5316</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2216</v>
+        <v>-0.6056</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8587</v>
+        <v>-2.1761</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6371</v>
+        <v>1.5705</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0773</v>
+        <v>0.2814</v>
       </c>
       <c r="N4" t="n">
-        <v>0.251</v>
+        <v>1.3203</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8264</v>
+        <v>-1.0389</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3451</v>
+        <v>-0.5503</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2994</v>
+        <v>-0.0678</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0457</v>
+        <v>-0.4826</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>4.3579</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>4.3579</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5993</v>
+        <v>2.3093</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1416</v>
+        <v>1.3127</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4577</v>
+        <v>0.9966</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3185</v>
+        <v>1.2998</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8542</v>
+        <v>1.106</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5357</v>
+        <v>0.1939</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5646</v>
+        <v>0.2072</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.1584</v>
+        <v>0.8479</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5938</v>
+        <v>-0.6407</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2461</v>
+        <v>1.0926</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3042</v>
+        <v>0.2581</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0581</v>
+        <v>0.8345</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9993</v>
+        <v>0.0291</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3962</v>
+        <v>0.0161</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6031</v>
+        <v>0.013</v>
       </c>
       <c r="V5" t="n">
-        <v>4.3707</v>
+        <v>-0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>4.3707</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>K. ZORIKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0685</v>
+        <v>1.5434</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9801</v>
+        <v>0.8</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0885</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6183999999999999</v>
+        <v>1.4472</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8769</v>
+        <v>2.0931</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2585</v>
+        <v>-0.6459</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2605</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.4106</v>
+        <v>-0.0312</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6711</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8789</v>
+        <v>0.9275</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5337</v>
+        <v>2.1244</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4126</v>
+        <v>-1.1968</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4355</v>
+        <v>-1.4666</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6684</v>
+        <v>-0.1443</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2329</v>
+        <v>-1.3223</v>
       </c>
       <c r="V6" t="n">
-        <v>2.0246</v>
+        <v>1.5628</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1853</v>
+        <v>1.5628</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. JIMENEZ</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1807</v>
+        <v>1.2715</v>
       </c>
       <c r="E7" t="n">
-        <v>0.962</v>
+        <v>1.4682</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2187</v>
+        <v>-0.1966</v>
       </c>
       <c r="G7" t="n">
-        <v>0.377</v>
+        <v>-0.6476</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4992</v>
+        <v>-0.9005</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1222</v>
+        <v>0.253</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5019</v>
+        <v>0.207</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9177999999999999</v>
+        <v>-1.4456</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4159</v>
+        <v>1.6527</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1249</v>
+        <v>-0.8546</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5814</v>
+        <v>0.5451</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7063</v>
+        <v>-1.3997</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4162</v>
+        <v>-0.3297</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2994</v>
+        <v>0.2203</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1167</v>
+        <v>-0.5501</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>2.0212</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. ZORIKS</t>
+          <t>M. JIMENEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1727</v>
+        <v>0.9507</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.5928</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1782</v>
+        <v>0.358</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4237</v>
+        <v>0.3772</v>
       </c>
       <c r="H8" t="n">
-        <v>2.082</v>
+        <v>1.5019</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6583</v>
+        <v>-1.1248</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5326</v>
+        <v>0.4886</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0244</v>
+        <v>0.9136</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5570000000000001</v>
+        <v>-0.4249</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8911</v>
+        <v>-0.1114</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1064</v>
+        <v>0.5884</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2153</v>
+        <v>-0.6998</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8259</v>
+        <v>0.1881</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0212</v>
+        <v>-0.0536</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.847</v>
+        <v>0.2418</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5748</v>
+        <v>0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5748</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4167</v>
+        <v>-0.9483</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6622</v>
+        <v>-1.3705</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2455</v>
+        <v>0.4222</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7605</v>
+        <v>1.7773</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2322</v>
+        <v>2.2371</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4717</v>
+        <v>-0.4598</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2322</v>
+        <v>1.2266</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1949</v>
+        <v>1.1893</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5283</v>
+        <v>0.5507</v>
       </c>
       <c r="N9" t="n">
-        <v>1.0373</v>
+        <v>1.0477</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5893</v>
+        <v>-1.1322</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6261</v>
+        <v>-0.3207</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9633</v>
+        <v>-0.8115</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6428</v>
+        <v>-1.3268</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2563</v>
+        <v>-0.9545</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3866</v>
+        <v>-0.3723</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7074</v>
+        <v>-0.7019</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1962</v>
+        <v>0.2008</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9036</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0077</v>
+        <v>0.0016</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5232</v>
+        <v>-0.2184</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5565</v>
+        <v>-0.251</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0333</v>
+        <v>0.0327</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2466</v>
+        <v>-2.9194</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4548</v>
+        <v>-2.0534</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.866</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9308</v>
+        <v>-0.9255</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7591</v>
+        <v>0.7528</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6899</v>
+        <v>-1.6783</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2309</v>
+        <v>0.2161</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1936</v>
+        <v>0.1789</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1617</v>
+        <v>-1.1416</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5655</v>
+        <v>0.574</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.728</v>
+        <v>-0.4005</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4174</v>
+        <v>0.0068</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3106</v>
+        <v>-0.4074</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8549</v>
+        <v>-4.0028</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3347</v>
+        <v>-0.6317</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5202</v>
+        <v>-3.3711</v>
       </c>
       <c r="G12" t="n">
-        <v>1.611</v>
+        <v>1.6213</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5785</v>
+        <v>2.5818</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9675</v>
+        <v>-0.9605</v>
       </c>
       <c r="J12" t="n">
-        <v>1.48</v>
+        <v>1.4734</v>
       </c>
       <c r="K12" t="n">
-        <v>1.368</v>
+        <v>1.3617</v>
       </c>
       <c r="L12" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>0.131</v>
+        <v>0.1479</v>
       </c>
       <c r="N12" t="n">
-        <v>1.2105</v>
+        <v>1.2201</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7361</v>
+        <v>-0.8988</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0907</v>
+        <v>-0.193</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8269</v>
+        <v>-0.7058</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.0492</v>
+        <v>-4.0424</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.209800000000001</v>
+        <v>8.2637</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2683</v>
+        <v>7.034700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9415000000000004</v>
+        <v>1.2292</v>
       </c>
       <c r="G13" t="n">
-        <v>12.1111</v>
+        <v>12.1679</v>
       </c>
       <c r="H13" t="n">
-        <v>17.3085</v>
+        <v>17.3045</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.1973</v>
+        <v>-5.1365</v>
       </c>
       <c r="J13" t="n">
-        <v>11.8776</v>
+        <v>11.673</v>
       </c>
       <c r="K13" t="n">
-        <v>7.1737</v>
+        <v>7.043699999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>4.704000000000001</v>
+        <v>4.6295</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2333000000000001</v>
+        <v>0.4948000000000002</v>
       </c>
       <c r="N13" t="n">
-        <v>10.1348</v>
+        <v>10.2608</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.901299999999999</v>
+        <v>-9.7659</v>
       </c>
       <c r="P13" t="n">
-        <v>3.33066907387547e-16</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.3417</v>
+        <v>-11.3817</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3417</v>
+        <v>11.3817</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.9542</v>
+        <v>-6.9435</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.4952</v>
+        <v>-1.4428</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.459200000000001</v>
+        <v>-5.5008</v>
       </c>
       <c r="V13" t="n">
-        <v>3.053100000000001</v>
+        <v>3.039199999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>8.227399999999999</v>
+        <v>8.186</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.174300000000001</v>
+        <v>-5.1467</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6174</v>
+        <v>4.4462</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3685</v>
+        <v>3.2297</v>
       </c>
       <c r="F14" t="n">
-        <v>1.249</v>
+        <v>1.2166</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7371</v>
+        <v>0.74</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2813</v>
+        <v>0.2842</v>
       </c>
       <c r="I14" t="n">
         <v>0.4558</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2928</v>
+        <v>1.2696</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4475</v>
+        <v>1.4339</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1547</v>
+        <v>-0.1643</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5557</v>
+        <v>-0.5296</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1662</v>
+        <v>-1.1497</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4947</v>
+        <v>1.3192</v>
       </c>
       <c r="T14" t="n">
-        <v>0.983</v>
+        <v>0.8706</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5117</v>
+        <v>0.4487</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3493</v>
+        <v>3.2427</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4747</v>
+        <v>2.344</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8986</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8424</v>
+        <v>0.8413</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.378</v>
+        <v>-1.3813</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2204</v>
+        <v>2.2226</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2282</v>
+        <v>1.2133</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6485</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8658</v>
+        <v>1.8618</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3858</v>
+        <v>-0.372</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>1.851</v>
+        <v>1.7397</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0858</v>
+        <v>0.9729</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7652</v>
+        <v>0.7667</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. DIALLO</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.747</v>
+        <v>0.5526</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6548</v>
+        <v>-0.9933</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9078000000000001</v>
+        <v>1.5459</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.9256</v>
+        <v>-0.9053</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3578</v>
+        <v>-1.4987</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5678</v>
+        <v>0.5934</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3167</v>
+        <v>-0.5493</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2393</v>
+        <v>-1.2108</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.6615</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6089</v>
+        <v>-0.356</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1185</v>
+        <v>-0.2879</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4904</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0731</v>
+        <v>1.1393</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5989</v>
+        <v>0.7428</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4742</v>
+        <v>0.3964</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5068</v>
+        <v>0.7739</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5068</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.673</v>
+        <v>0.1191</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9335</v>
+        <v>0.3665</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6065</v>
+        <v>-0.2474</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8734</v>
+        <v>-0.7285</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.489</v>
+        <v>-0.8851</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6156</v>
+        <v>0.1566</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4959</v>
+        <v>0.1462</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1886</v>
+        <v>0.0345</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6928</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3776</v>
+        <v>-0.8747</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3003</v>
+        <v>-0.9196</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0772</v>
+        <v>0.0449</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2288</v>
+        <v>0.3924</v>
       </c>
       <c r="T17" t="n">
-        <v>0.738</v>
+        <v>0.2203</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4908</v>
+        <v>0.1721</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>H. DIALLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4404</v>
+        <v>-0.1076</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9540999999999999</v>
+        <v>1.0333</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5138</v>
+        <v>-1.1409</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7428</v>
+        <v>-1.926</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8948</v>
+        <v>-1.3585</v>
       </c>
       <c r="I18" t="n">
-        <v>0.152</v>
+        <v>-0.5675</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1466</v>
+        <v>-0.3342</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0346</v>
+        <v>-0.252</v>
       </c>
       <c r="L18" t="n">
-        <v>0.112</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8894</v>
+        <v>-1.5918</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9294</v>
+        <v>-1.1064</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04</v>
+        <v>-0.4854</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7295</v>
+        <v>0.2345</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8075</v>
+        <v>0.0112</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.078</v>
+        <v>0.2232</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.4945</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.4945</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1955</v>
+        <v>-0.8184</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0087</v>
+        <v>2.5245</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2042</v>
+        <v>-3.3429</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7664</v>
+        <v>3.819</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6032</v>
+        <v>-2.5306</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3697</v>
+        <v>6.3495</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4695</v>
+        <v>4.5342</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6651</v>
+        <v>-2.0414</v>
       </c>
       <c r="L19" t="n">
-        <v>3.1346</v>
+        <v>6.5756</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.703</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0619</v>
+        <v>-0.4891</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7649</v>
+        <v>-0.226</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.3123</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8075</v>
+        <v>0.2666</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0378</v>
+        <v>0.0457</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.278</v>
+        <v>-3.584</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.278</v>
+        <v>-3.584</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6366</v>
+        <v>-1.4935</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7814</v>
+        <v>0.5214</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1448</v>
+        <v>-2.0148</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.919</v>
+        <v>1.7739</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.919</v>
+        <v>-0.5977</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2.3716</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5727</v>
+        <v>2.4589</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.5727</v>
+        <v>-0.669</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.1279</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3463</v>
+        <v>-0.6851</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3463</v>
+        <v>0.0713</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.7563</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0556</v>
+        <v>0.4564</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2087</v>
+        <v>0.3388</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2643</v>
+        <v>0.1176</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-3.2684</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9754</v>
+        <v>-1.5292</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5028</v>
+        <v>-1.5515</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4782</v>
+        <v>0.0223</v>
       </c>
       <c r="G21" t="n">
-        <v>3.8298</v>
+        <v>-1.924</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.5353</v>
+        <v>-1.924</v>
       </c>
       <c r="I21" t="n">
-        <v>6.3652</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5696</v>
+        <v>-1.5793</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.0301</v>
+        <v>-1.5793</v>
       </c>
       <c r="L21" t="n">
-        <v>6.5997</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7398</v>
+        <v>-0.3447</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5053</v>
+        <v>-0.3447</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2345</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8447</v>
+        <v>0.1672</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7984</v>
+        <v>0.0278</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0463</v>
+        <v>0.1394</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.5994</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.5994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8746</v>
+        <v>-1.8095</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0381</v>
+        <v>-0.2532</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8364</v>
+        <v>-1.5563</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0279</v>
+        <v>-2.0441</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4071</v>
+        <v>-0.3969</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6209</v>
+        <v>-1.6472</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4004</v>
+        <v>-0.4407</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2322</v>
+        <v>-0.2381</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1682</v>
+        <v>-0.2026</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6275</v>
+        <v>-1.6034</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5933</v>
+        <v>-0.5181</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7984</v>
+        <v>0.0297</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7948</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.209</v>
+        <v>-4.1751</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6678</v>
+        <v>-3.2828</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5411</v>
+        <v>-0.8922</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3608</v>
+        <v>-3.3596</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5266</v>
+        <v>-2.5301</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8343</v>
+        <v>-0.8295</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1042</v>
+        <v>-1.1245</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.0372</v>
+        <v>-2.0554</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9329</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.2566</v>
+        <v>-2.2351</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7672</v>
+        <v>-1.7604</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4202</v>
+        <v>1.4608</v>
       </c>
       <c r="T23" t="n">
-        <v>1.8389</v>
+        <v>1.2561</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5813</v>
+        <v>0.2047</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1458</v>
+        <v>-5.6456</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4842</v>
+        <v>-5.1676</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6616</v>
+        <v>-0.478</v>
       </c>
       <c r="G24" t="n">
-        <v>-8.437200000000001</v>
+        <v>-8.454599999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.4788</v>
+        <v>-4.4858</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.9584</v>
+        <v>-3.9688</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.0502</v>
+        <v>-6.0892</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.014</v>
+        <v>-3.0347</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.0362</v>
+        <v>-3.0545</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.387</v>
+        <v>-2.3654</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7697000000000001</v>
+        <v>1.2855</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4053</v>
+        <v>0.7638</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3644</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.209800000000001</v>
+        <v>-7.2183</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9414000000000007</v>
+        <v>-1.229</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.2683</v>
+        <v>-5.989100000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-12.111</v>
+        <v>-12.1679</v>
       </c>
       <c r="H25" t="n">
-        <v>-17.3083</v>
+        <v>-17.3045</v>
       </c>
       <c r="I25" t="n">
-        <v>5.197299999999999</v>
+        <v>5.136500000000002</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2334000000000014</v>
+        <v>-0.4950000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-10.1347</v>
+        <v>-10.2608</v>
       </c>
       <c r="L25" t="n">
-        <v>9.901399999999999</v>
+        <v>9.765899999999998</v>
       </c>
       <c r="M25" t="n">
-        <v>-11.8776</v>
+        <v>-11.673</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.1736</v>
+        <v>-7.043500000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.7039</v>
+        <v>-4.6293</v>
       </c>
       <c r="P25" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-0.0001000000000004331</v>
       </c>
       <c r="Q25" t="n">
-        <v>-11.3416</v>
+        <v>-11.3816</v>
       </c>
       <c r="R25" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S25" t="n">
-        <v>7.9543</v>
+        <v>7.9892</v>
       </c>
       <c r="T25" t="n">
-        <v>5.4594</v>
+        <v>5.5006</v>
       </c>
       <c r="U25" t="n">
-        <v>2.495</v>
+        <v>2.4883</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.0531</v>
+        <v>-3.039300000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>5.174300000000001</v>
+        <v>5.1469</v>
       </c>
       <c r="X25" t="n">
-        <v>-8.2273</v>
+        <v>-8.1859</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104508_W6.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104508_W6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-5.1467</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-3.584</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104508_W6.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-8.1859</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
